--- a/artfynd/A 58470-2023 artfynd.xlsx
+++ b/artfynd/A 58470-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122633084</v>
       </c>
       <c r="B2" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 58470-2023 artfynd.xlsx
+++ b/artfynd/A 58470-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122633084</v>
       </c>
       <c r="B2" t="n">
-        <v>90852</v>
+        <v>90855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 58470-2023 artfynd.xlsx
+++ b/artfynd/A 58470-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122633084</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 58470-2023 artfynd.xlsx
+++ b/artfynd/A 58470-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122633084</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
